--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Category.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Category.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fertilizante</t>
+          <t>Adubo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chão</t>
+          <t>Piso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -960,61 +960,61 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>floor_field</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.306</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fundação</t>
+          <t>Campo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎</t>
+          <t>畑</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>obj</t>
+          <t>floor_deco</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alpha 20.40</t>
+          <t>EA 23.306</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Item Decorativo</t>
+          <t>Decoração de Piso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Prop</t>
+          <t>Floor Decoration</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>小道具</t>
+          <t>床装飾</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>foundation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1024,105 +1024,105 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comida</t>
+          <t>Fundação</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>食料</t>
+          <t>基礎</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meal</t>
+          <t>obj</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Refeição</t>
+          <t>Adereço</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Meal</t>
+          <t>Prop</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>料理</t>
+          <t>小道具</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meal_meat</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Refeição de Carne</t>
+          <t>Comida</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Meat Meal</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>肉料理</t>
+          <t>食料</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>meal_fish</t>
+          <t>meal</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Refeição de Peixe</t>
+          <t>Refeição</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fish Meal</t>
+          <t>Meal</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>魚料理</t>
+          <t>料理</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>meal_vegi</t>
+          <t>meal_meat</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1132,24 +1132,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Refeição de Legumes</t>
+          <t>Refeição de Carne</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vegetable Meal</t>
+          <t>Meat Meal</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>野菜料理</t>
+          <t>肉料理</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meal_fruit</t>
+          <t>meal_fish</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1159,24 +1159,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Refeição de Frutas</t>
+          <t>Refeição de Peixe</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fruit Meal</t>
+          <t>Fish Meal</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>果物料理</t>
+          <t>魚料理</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meal_cake</t>
+          <t>meal_vegi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolo</t>
+          <t>Refeição de Vegetais</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cake</t>
+          <t>Vegetable Meal</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ケーキ</t>
+          <t>野菜料理</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>meal_bread</t>
+          <t>meal_fruit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1213,51 +1213,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pão</t>
+          <t>Refeição de Frutas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Fruit Meal</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>パン</t>
+          <t>果物料理</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>meal_cookie</t>
+          <t>meal_cake</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alpha 18.1</t>
+          <t>Alpha 17.1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Biscoito</t>
+          <t>Bolo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cookie</t>
+          <t>Cake</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>クッキー</t>
+          <t>ケーキ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meal_noodle</t>
+          <t>meal_bread</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1267,51 +1267,51 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Macarrão</t>
+          <t>Pão</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Noodle</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ヌードル</t>
+          <t>パン</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>meal_egg</t>
+          <t>meal_cookie</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>Alpha 18.1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Refeição de Ovo</t>
+          <t>Bolacha</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Egg Meal</t>
+          <t>Cookie</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>卵料理</t>
+          <t>クッキー</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>meal_rice</t>
+          <t>meal_noodle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1321,24 +1321,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Refeição de Arroz</t>
+          <t>Macarrão</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rice Meal</t>
+          <t>Noodle</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ご飯物</t>
+          <t>ヌードル</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>meal_soup</t>
+          <t>meal_egg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1348,186 +1348,186 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sopa</t>
+          <t>Refeição de Ovo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Soup</t>
+          <t>Egg Meal</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>スープ</t>
+          <t>卵料理</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>meal_lunch</t>
+          <t>meal_rice</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EA 23.183</t>
+          <t>Alpha 17.1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Almoço</t>
+          <t>Refeição de Arroz</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Rice Meal</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ランチ</t>
+          <t>ご飯物</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>foodstuff</t>
+          <t>meal_soup</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 17.1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Comida em Geral</t>
+          <t>Sopa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Foodstuff</t>
+          <t>Soup</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>食材</t>
+          <t>スープ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>grain</t>
+          <t>meal_lunch</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Beta 22.41</t>
+          <t>EA 23.183</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Grãos</t>
+          <t>Almoço</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>穀物</t>
+          <t>ランチ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dough</t>
+          <t>foodstuff</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EA 23.16</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Massa</t>
+          <t>Mantimento</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Dough</t>
+          <t>Foodstuff</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>練り粉</t>
+          <t>食材</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>meat</t>
+          <t>grain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Beta 22.41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Carne</t>
+          <t>Grão</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>肉</t>
+          <t>穀物</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vegi</t>
+          <t>dough</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Legume</t>
+          <t>Massa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Dough</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>野菜</t>
+          <t>練り粉</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fruit</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1537,132 +1537,132 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fruta</t>
+          <t>Carne</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>果物</t>
+          <t>肉</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>vegi</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cogumelo</t>
+          <t>Vegetal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>きのこ</t>
+          <t>野菜</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>egg</t>
+          <t>fruit</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Beta 22.41</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Fruta</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Egg</t>
+          <t>Fruit</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>卵</t>
+          <t>果物</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Cogumelo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>魚</t>
+          <t>きのこ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nuts</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Beta 22.41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nozes</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Nuts</t>
+          <t>Egg</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>実</t>
+          <t>卵</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>seasoning</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1672,240 +1672,240 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tempero</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Seasoning</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>調味料</t>
+          <t>魚</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>_seasoning</t>
+          <t>nuts</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Beta 22.41</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempero</t>
+          <t>Castanhas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Seasoning</t>
+          <t>Nuts</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>調味料</t>
+          <t>実</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>herb</t>
+          <t>filling</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EA 23.8</t>
+          <t>EA 23.319</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Erva</t>
+          <t>Recheio</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Herb</t>
+          <t>Filling</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ハーブ</t>
+          <t>フィリング</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sauce</t>
+          <t>seasoning</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Molho</t>
+          <t>Tempero</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sauce</t>
+          <t>Seasoning</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ソース</t>
+          <t>調味料</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>spice</t>
+          <t>_seasoning</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Beta 22.41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Especiaria</t>
+          <t>Tempero</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Spice</t>
+          <t>Seasoning</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>スパイス</t>
+          <t>調味料</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>preserved</t>
+          <t>herb</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.8</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Comida Conservada</t>
+          <t>Erva</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Preserved Food</t>
+          <t>Herb</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>保存食</t>
+          <t>ハーブ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>foodstuff_raw</t>
+          <t>sauce</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Comida Crua</t>
+          <t>Molho</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Raw Foodstuff</t>
+          <t>Sauce</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>未加工食材</t>
+          <t>ソース</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>drink</t>
+          <t>spice</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bebida</t>
+          <t>Especiaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Drink</t>
+          <t>Spice</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>飲料</t>
+          <t>スパイス</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>_drink</t>
+          <t>preserved</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Beta 22.58</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poção</t>
+          <t>Comida Conservada</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Potion</t>
+          <t>Preserved Food</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ポーション</t>
+          <t>保存食</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>booze</t>
+          <t>foodstuff_raw</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1915,132 +1915,132 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Álcool</t>
+          <t>Mantimento Cru</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Booze</t>
+          <t>Raw Foodstuff</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>酒</t>
+          <t>未加工食材</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>drink</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alpha 20.43</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Leite</t>
+          <t>Bebida</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Drink</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ミルク</t>
+          <t>飲料</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>drug</t>
+          <t>_drink</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Beta 22.58</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Droga</t>
+          <t>Poção</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Drug</t>
+          <t>Potion</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>薬</t>
+          <t>ポーション</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>booze</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arma</t>
+          <t>Trago</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Booze</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>武器</t>
+          <t>酒</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>Alpha 20.43</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Corpo a Corpo</t>
+          <t>Laticínio</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Melee Weapon</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>近接武器</t>
+          <t>ミルク</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sword</t>
+          <t>drug</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2050,105 +2050,105 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Espada Longa</t>
+          <t>Droga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Long Sword</t>
+          <t>Drug</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>長剣</t>
+          <t>薬</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dagger</t>
+          <t>weapon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 17.1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Espada Curta</t>
+          <t>Arma</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Short Sword</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>短剣</t>
+          <t>武器</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>blunt</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 17.1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arma Contundente</t>
+          <t>Arma Corpo a Corpo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Blunt Weapon</t>
+          <t>Melee Weapon</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>鈍器</t>
+          <t>近接武器</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>sword</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cajado</t>
+          <t>Espada Longa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>Long Sword</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>杖</t>
+          <t>長剣</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>axe</t>
+          <t>dagger</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2158,24 +2158,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Machado</t>
+          <t>Espada Curta</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Axe</t>
+          <t>Short Sword</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>斧</t>
+          <t>短剣</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>polearm</t>
+          <t>blunt</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2185,78 +2185,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arma de Lança</t>
+          <t>Arma Contundente</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Polearm</t>
+          <t>Blunt Weapon</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>棒</t>
+          <t>鈍器</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>scythe</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Foice</t>
+          <t>Cajado</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Scythe</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>鎌</t>
+          <t>杖</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>martial</t>
+          <t>axe</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EA 23.8</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Arma Marcial</t>
+          <t>Machado</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Martial Weapon</t>
+          <t>Axe</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>暗器</t>
+          <t>斧</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ranged</t>
+          <t>polearm</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2266,24 +2266,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Arma de Longo Alcance</t>
+          <t>Arma de Haste</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ranged Weapon</t>
+          <t>Polearm</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>射撃武器</t>
+          <t>棒</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ammo</t>
+          <t>scythe</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2293,51 +2293,51 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Munição</t>
+          <t>Foice</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ammo</t>
+          <t>Scythe</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>矢弾</t>
+          <t>鎌</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bow</t>
+          <t>martial</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.8</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arco</t>
+          <t>Arma Marcial</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Martial Weapon</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>弓</t>
+          <t>暗器</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>crossbow</t>
+          <t>ranged</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2347,24 +2347,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Besta</t>
+          <t>Arma à Distância</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Crossbow</t>
+          <t>Ranged Weapon</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>クロスボウ</t>
+          <t>射撃武器</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>gun</t>
+          <t>ammo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2374,78 +2374,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arma de Fogo</t>
+          <t>Munição</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Gun</t>
+          <t>Ammo</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>銃</t>
+          <t>矢弾</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cane</t>
+          <t>bow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alpha 20.65</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cajado</t>
+          <t>Arco</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cane</t>
+          <t>Bow</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ワンド</t>
+          <t>弓</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>throw</t>
+          <t>crossbow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alpha 20.50</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arma de Arremesso</t>
+          <t>Besta</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Throwing Weapon</t>
+          <t>Crossbow</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>投擲武器</t>
+          <t>クロスボウ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>gun</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2455,78 +2455,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Armadura</t>
+          <t>Arma de Fogo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Gun</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>防具</t>
+          <t>銃</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>torso</t>
+          <t>cane</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.65</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Equipamento de Torso</t>
+          <t>Bengala</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Torso Gear</t>
+          <t>Cane</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>胴装備</t>
+          <t>ワンド</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>throw</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.50</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Equipamento de Cabeça</t>
+          <t>Arma de Arremesso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Head Gear</t>
+          <t>Throwing Weapon</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>頭装備</t>
+          <t>投擲武器</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2536,24 +2536,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Equipamento de Costas</t>
+          <t>Armadura</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Back Gear</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>背中装備</t>
+          <t>防具</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>waist</t>
+          <t>torso</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2563,24 +2563,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Equipamento de Cintura</t>
+          <t>Equipamento de Torso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Waist Gear</t>
+          <t>Torso Gear</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>腰装備</t>
+          <t>胴装備</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>arm</t>
+          <t>head</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2590,24 +2590,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Equipamento de Braços</t>
+          <t>Equipamento de Cabeça</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Arm Gear</t>
+          <t>Head Gear</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>腕装備</t>
+          <t>頭装備</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>foot</t>
+          <t>back</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2617,24 +2617,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Equipamento de Pés</t>
+          <t>Equipamento de Costas</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Foot Gear</t>
+          <t>Back Gear</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>足装備</t>
+          <t>背中装備</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>finger</t>
+          <t>waist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2644,24 +2644,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Equipamento de Dedos</t>
+          <t>Equipamento de Cintura</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Finger Gear</t>
+          <t>Waist Gear</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>指装備</t>
+          <t>腰装備</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>arm</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2671,24 +2671,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Anel</t>
+          <t>Equipamento de Braços</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ring</t>
+          <t>Arm Gear</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>指輪</t>
+          <t>腕装備</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>neck</t>
+          <t>foot</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2698,24 +2698,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Equipamento de Pescoço</t>
+          <t>Equipamento de Pés</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Neck Gear</t>
+          <t>Foot Gear</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>首装備</t>
+          <t>足装備</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>amulet</t>
+          <t>finger</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2725,24 +2725,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Amuleto</t>
+          <t>Equipamento de Dedos</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Amulet</t>
+          <t>Finger Gear</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>首輪</t>
+          <t>指装備</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>shield</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2752,24 +2752,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Escudo</t>
+          <t>Anel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Ring</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>盾</t>
+          <t>指輪</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>toolbelt</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2779,24 +2779,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cinto de Ferramentas</t>
+          <t>Equipamento de Pescoço</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Toolbelt</t>
+          <t>Neck Gear</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ツールベルト</t>
+          <t>首装備</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lightsource</t>
+          <t>amulet</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fonte de Luz</t>
+          <t>Amuleto</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Light Source</t>
+          <t>Amulet</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>光源</t>
+          <t>首輪</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2833,51 +2833,51 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Móveis</t>
+          <t>Escudo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>家具</t>
+          <t>盾</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>_furniture</t>
+          <t>toolbelt</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Beta 22.41</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Móveis</t>
+          <t>Cinto de Ferramentas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Toolbelt</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>家具</t>
+          <t>ツールベルト</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>container</t>
+          <t>lightsource</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2887,51 +2887,51 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Container</t>
+          <t>Fonte de Luz</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Container</t>
+          <t>Light Source</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>コンテナ</t>
+          <t>光源</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>relic</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.340</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Janela</t>
+          <t>Relíquia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Relic</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>窓</t>
+          <t>遺物</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2941,51 +2941,51 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iluminação</t>
+          <t>Móvel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>照明</t>
+          <t>家具</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>deco</t>
+          <t>_furniture</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Beta 22.41</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Decoração</t>
+          <t>Móvel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>装飾</t>
+          <t>家具</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>plantpot</t>
+          <t>container</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2995,24 +2995,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Vaso de Planta</t>
+          <t>Contêiner</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Plant Pot</t>
+          <t>Container</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>鉢植え</t>
+          <t>コンテナ</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>window</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3022,105 +3022,105 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Instalação</t>
+          <t>Janela</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>設備</t>
+          <t>窓</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>crafter</t>
+          <t>light</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oficineiro</t>
+          <t>Iluminação</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Crafter</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>製作設備</t>
+          <t>照明</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>processor</t>
+          <t>deco</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Processador</t>
+          <t>Decoração</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Processor</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>加工設備</t>
+          <t>装飾</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>generator</t>
+          <t>plantpot</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alpha 21.11</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gerador</t>
+          <t>Vaso de Planta</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Generator</t>
+          <t>Plant Pot</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>発電機</t>
+          <t>鉢植え</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mount</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3130,105 +3130,105 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Instalação</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Hanging</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>マウント</t>
+          <t>設備</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ext</t>
+          <t>crafter</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alpha 21.11</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Exterior</t>
+          <t>Fabricador</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Exterior</t>
+          <t>Crafter</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>屋外用品</t>
+          <t>製作設備</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mech</t>
+          <t>processor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mecânica</t>
+          <t>Processador</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mech</t>
+          <t>Processor</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>機工</t>
+          <t>加工設備</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>generator</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alpha 21.1</t>
+          <t>Alpha 21.11</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Utilitário</t>
+          <t>Gerador</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Generator</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>特殊</t>
+          <t>発電機</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>bed</t>
+          <t>mount</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3238,51 +3238,51 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cama</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Bed</t>
+          <t>Hanging</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ベッド</t>
+          <t>マウント</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ext</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 21.11</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cadeira</t>
+          <t>Exterior</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>Exterior</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>椅子</t>
+          <t>屋外用品</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>mech</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3292,105 +3292,105 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Mecanismo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Mech</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>机</t>
+          <t>機工</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>door</t>
+          <t>util</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 21.1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Porta</t>
+          <t>Utilitário</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>扉</t>
+          <t>特殊</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>bed</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Alpha 20.40</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Cama</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Bed</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>カード</t>
+          <t>ベッド</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>figure</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Alpha 12.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Figura</t>
+          <t>Cadeira</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>フィギア</t>
+          <t>椅子</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>table</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3400,213 +3400,213 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>アイテム</t>
+          <t>机</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>_item</t>
+          <t>door</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Beta 22.41</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Porta</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>アイテム</t>
+          <t>扉</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rune</t>
+          <t>card</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EA 23.90</t>
+          <t>Alpha 20.40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Runa</t>
+          <t>Carta</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ルーン</t>
+          <t>カード</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>mod</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EA 23.90</t>
+          <t>Alpha 12.1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Modificação</t>
+          <t>Boneco</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mod</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>改造道具</t>
+          <t>フィギア</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bait</t>
+          <t>item</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Alpha 20.7</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Isca</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Bait</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>餌</t>
+          <t>アイテム</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>_item</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Beta 22.41</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Livro</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>本</t>
+          <t>アイテム</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>_book</t>
+          <t>rune</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Beta 22.41</t>
+          <t>EA 23.90</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Livro</t>
+          <t>Runa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Rune</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>本</t>
+          <t>ルーン</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>scroll</t>
+          <t>mod</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.90</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pergaminho</t>
+          <t>Mod</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>Mod</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>巻物</t>
+          <t>改造道具</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ancientbook</t>
+          <t>bait</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3616,24 +3616,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Livro Antigo</t>
+          <t>Isca</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ancient Book</t>
+          <t>Bait</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>古の書</t>
+          <t>餌</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>spellbook</t>
+          <t>book</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3643,51 +3643,51 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Livro de Feitiços</t>
+          <t>Livro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Spell Book</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>魔法書</t>
+          <t>本</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>skillbook</t>
+          <t>_book</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Beta 22.41</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Livro de Habilidades</t>
+          <t>Livro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Skill Book</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>技術書</t>
+          <t>本</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>scroll</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3697,51 +3697,51 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mapa</t>
+          <t>Pergaminho</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>地図</t>
+          <t>巻物</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ancientbook</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>Alpha 20.7</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Livro Antigo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Ancient Book</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>古の書</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>junk</t>
+          <t>spellbook</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3751,105 +3751,105 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sucata</t>
+          <t>Livro de Feitiços</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Junk</t>
+          <t>Spell Book</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ジャンク</t>
+          <t>魔法書</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>globe</t>
+          <t>skillbook</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Alpha 20.7</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Globo</t>
+          <t>Livro de Perícias</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Globe</t>
+          <t>Skill Book</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>地球儀</t>
+          <t>技術書</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>pot</t>
+          <t>map</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Alpha 20.7</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Vaso</t>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Pot</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>鍋</t>
+          <t>地図</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>souvenir</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Lembrança</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Souvenir</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>お土産</t>
+          <t>その他</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>garbage</t>
+          <t>junk</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3859,78 +3859,78 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lixo</t>
+          <t>Traste</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Garbage</t>
+          <t>Junk</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ゴミ</t>
+          <t>ジャンク</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>chara</t>
+          <t>globe</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.7</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Personagem</t>
+          <t>Globo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Chara</t>
+          <t>Globe</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>キャラ</t>
+          <t>地球儀</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>bill</t>
+          <t>pot</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.7</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Conta</t>
+          <t>Panela</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Pot</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>請求書</t>
+          <t>鍋</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>valuable</t>
+          <t>souvenir</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3940,24 +3940,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valioso</t>
+          <t>Lembrança</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Valuable</t>
+          <t>Souvenir</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>貴重品</t>
+          <t>お土産</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ability</t>
+          <t>garbage</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3967,51 +3967,51 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Habilidade</t>
+          <t>Lixo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ability</t>
+          <t>Garbage</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>アビリティー</t>
+          <t>ゴミ</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>trap</t>
+          <t>chara</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Alpha 12.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Armadilha</t>
+          <t>Personagem</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Trap</t>
+          <t>Chara</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>罠</t>
+          <t>キャラ</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tool</t>
+          <t>bill</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4021,51 +4021,51 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ferramenta</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ツール</t>
+          <t>請求書</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>_tool</t>
+          <t>valuable</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Beta 22.41</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ferramenta</t>
+          <t>Valioso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Valuable</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ツール</t>
+          <t>貴重品</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>ability</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4075,96 +4075,204 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Instrumento</t>
+          <t>Habilidade</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Instrument</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>楽器</t>
+          <t>アビリティー</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rod</t>
+          <t>trap</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EA 23.36</t>
+          <t>Alpha 12.1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Varinha</t>
+          <t>Armadilha</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Rod</t>
+          <t>Trap</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>魔法杖</t>
+          <t>罠</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>catalyst</t>
+          <t>tool</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Alpha 20.27</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Catalisador</t>
+          <t>Ferramenta</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Catalyst</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>触媒</t>
+          <t>ツール</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>_tool</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Beta 22.41</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ferramenta</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Alpha 11.1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Instrumento</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>rod</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EA 23.36</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Varinha</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Rod</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>魔法杖</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>catalyst</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Alpha 20.27</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Catalisador</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>触媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Alpha 11.1</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Alpha 11.1</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>Moeda</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>通貨</t>
         </is>
